--- a/K9HZ_Antenna_Tuner/K9HZ_Antenna_Tuner_BOMs/K9HZ_100W_Antenna_Tuner_BOM_012826.xlsx
+++ b/K9HZ_Antenna_Tuner/K9HZ_Antenna_Tuner_BOMs/K9HZ_100W_Antenna_Tuner_BOM_012826.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\K9HZ\K9HZ_Antenna_Tuner\K9HZ_Antenna_Tuner_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325A40D9-36BB-4EA3-903B-376B4EA917D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C146246F-A757-401B-AC28-C522099E7406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{D1A16F5F-C85E-4895-AC46-7D6591F3EE2A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{D1A16F5F-C85E-4895-AC46-7D6591F3EE2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined" sheetId="7" r:id="rId1"/>
@@ -683,6 +683,66 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>615950</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1809750</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF3DCAA0-D86B-7569-B278-74E20B618A33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6553200" y="3454400"/>
+          <a:ext cx="2044700" cy="355600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1176,7 +1236,7 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
     </row>
-    <row r="10" spans="1:7" ht="84.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>27</v>
       </c>
